--- a/public/test-lock-assignments.xlsx
+++ b/public/test-lock-assignments.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cheny128\Desktop\For work\000SA\15统计学&amp;AI\智能决策项目\0421后迭代\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cheny128\Desktop\For work\000SA\15统计学&amp;AI\智能决策项目\0421后迭代\BC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60367966-CF7F-4A14-8B9D-6F11AF374397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB196E6-3C47-44EA-9D94-E79F8D1B4B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21495" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="锁定清单" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>inscode</t>
   </si>
@@ -42,28 +42,6 @@
   </si>
   <si>
     <t>产品组</t>
-  </si>
-  <si>
-    <t>SH029</t>
-  </si>
-  <si>
-    <t>LC_LEL20苏颖</t>
-  </si>
-  <si>
-    <t>GDGZ280</t>
-  </si>
-  <si>
-    <t>LC_LEL30林锦浩</t>
-  </si>
-  <si>
-    <t>BJ227</t>
-  </si>
-  <si>
-    <t>LC_LEL02吕京京</t>
-  </si>
-  <si>
-    <t>LC策略产品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -448,15 +426,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -467,41 +445,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="14.25" x14ac:dyDescent="0.15"/>
-    <row r="6" spans="1:3" ht="14.25" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
